--- a/data/trans_camb/P37-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P37-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 5,39</t>
+          <t>-0,55; 5,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,78</t>
+          <t>-1,05; 4,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,86</t>
+          <t>-2,81; 5,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,3</t>
+          <t>-1,52; 3,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,7</t>
+          <t>-0,86; 3,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 16,21</t>
+          <t>5,65; 16,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,5</t>
+          <t>-0,01; 3,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,39</t>
+          <t>-0,42; 3,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,3</t>
+          <t>2,06; 8,18</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 212,01</t>
+          <t>-12,38; 237,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 184,85</t>
+          <t>-25,55; 188,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 200,46</t>
+          <t>-68,21; 192,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,3; 212,09</t>
+          <t>-50,6; 205,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 287,03</t>
+          <t>-33,34; 263,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>155,11; 1106,78</t>
+          <t>155,3; 1050,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 154,18</t>
+          <t>-1,77; 168,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 139,37</t>
+          <t>-12,64; 143,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,99; 330,92</t>
+          <t>51,73; 348,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,02</t>
+          <t>-0,81; 4,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,85</t>
+          <t>-2,66; 1,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 11,27</t>
+          <t>2,8; 11,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,26</t>
+          <t>-0,6; 4,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,84</t>
+          <t>-1,78; 2,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 15,14</t>
+          <t>4,95; 15,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,28</t>
+          <t>-0,31; 3,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,58</t>
+          <t>-1,76; 1,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,35; 11,94</t>
+          <t>5,63; 12,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 110,16</t>
+          <t>-15,56; 124,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 59,0</t>
+          <t>-48,41; 54,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,65; 315,67</t>
+          <t>47,54; 303,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 157,03</t>
+          <t>-15,17; 160,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 114,47</t>
+          <t>-36,68; 120,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>102,29; 546,48</t>
+          <t>109,85; 553,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 94,57</t>
+          <t>-6,53; 85,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 47,01</t>
+          <t>-34,07; 48,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>111,53; 338,21</t>
+          <t>117,95; 340,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,68</t>
+          <t>-0,83; 4,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -0,62</t>
+          <t>-5,12; -0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,5</t>
+          <t>6,8; 14,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,4</t>
+          <t>-1,78; 3,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,87</t>
+          <t>-2,55; 2,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 13,17</t>
+          <t>6,34; 12,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,3</t>
+          <t>-0,69; 3,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,44</t>
+          <t>-3,1; 0,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,53</t>
+          <t>7,54; 12,32</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 113,97</t>
+          <t>-13,43; 111,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,53; -13,52</t>
+          <t>-73,49; -11,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98,73; 349,6</t>
+          <t>98,07; 340,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 67,37</t>
+          <t>-25,43; 65,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,49; 58,82</t>
+          <t>-33,43; 52,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79,78; 269,07</t>
+          <t>76,12; 249,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 65,09</t>
+          <t>-9,71; 64,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 8,86</t>
+          <t>-45,52; 3,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>105,71; 240,16</t>
+          <t>108,34; 244,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 4,42</t>
+          <t>-2,53; 4,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,88</t>
+          <t>-2,83; 3,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 14,31</t>
+          <t>-1,47; 14,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,25</t>
+          <t>-1,12; 4,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,67</t>
+          <t>-0,8; 4,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,54; 19,99</t>
+          <t>12,11; 19,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,64</t>
+          <t>-0,68; 4,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,56</t>
+          <t>-0,96; 3,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 15,76</t>
+          <t>3,7; 15,75</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 73,79</t>
+          <t>-28,67; 81,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 65,07</t>
+          <t>-32,1; 62,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 214,68</t>
+          <t>-12,58; 229,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 134,98</t>
+          <t>-19,34; 132,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 124,1</t>
+          <t>-13,13; 128,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>189,28; 532,89</t>
+          <t>168,87; 527,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 68,25</t>
+          <t>-8,69; 77,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 66,6</t>
+          <t>-12,51; 62,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>64,33; 277,47</t>
+          <t>58,01; 280,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 6,22</t>
+          <t>-4,77; 6,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 5,57</t>
+          <t>-4,75; 5,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,83; 23,6</t>
+          <t>13,15; 23,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 6,44</t>
+          <t>-3,99; 6,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 4,56</t>
+          <t>-5,89; 4,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,35; 24,23</t>
+          <t>14,2; 23,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 4,95</t>
+          <t>-2,45; 5,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 3,47</t>
+          <t>-3,5; 3,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,12; 22,37</t>
+          <t>15,0; 22,22</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 38,48</t>
+          <t>-21,36; 39,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 36,29</t>
+          <t>-22,96; 36,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56,91; 149,27</t>
+          <t>58,65; 152,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 42,39</t>
+          <t>-19,75; 44,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 31,16</t>
+          <t>-28,66; 31,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,96; 165,52</t>
+          <t>64,21; 164,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 31,36</t>
+          <t>-12,49; 32,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 22,15</t>
+          <t>-17,86; 22,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>74,15; 143,23</t>
+          <t>72,95; 143,15</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>9,58; 25,5</t>
+          <t>9,92; 25,94</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 14,76</t>
+          <t>-1,14; 14,88</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26,67; 40,66</t>
+          <t>26,34; 40,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 10,54</t>
+          <t>-4,46; 10,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 6,21</t>
+          <t>-8,93; 5,63</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,84; 50,73</t>
+          <t>26,78; 51,13</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,9; 15,69</t>
+          <t>4,6; 15,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 8,18</t>
+          <t>-2,9; 7,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>29,48; 47,44</t>
+          <t>29,59; 47,55</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22,82; 73,03</t>
+          <t>22,66; 74,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 42,16</t>
+          <t>-2,61; 43,11</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>58,73; 116,85</t>
+          <t>59,54; 115,29</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 25,66</t>
+          <t>-9,28; 26,08</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 15,16</t>
+          <t>-18,65; 13,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,07; 132,0</t>
+          <t>58,18; 134,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,03; 40,03</t>
+          <t>10,18; 39,16</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 20,89</t>
+          <t>-6,51; 19,49</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65,84; 118,59</t>
+          <t>68,06; 123,26</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 10,27</t>
+          <t>-8,26; 9,82</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 6,95</t>
+          <t>-8,89; 6,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12,93; 27,27</t>
+          <t>13,61; 27,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 10,76</t>
+          <t>-4,5; 10,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 5,61</t>
+          <t>-9,49; 5,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,82; 30,75</t>
+          <t>19,34; 31,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 7,54</t>
+          <t>-3,52; 8,11</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 4,17</t>
+          <t>-7,61; 4,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18,56; 27,94</t>
+          <t>18,45; 27,48</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 16,37</t>
+          <t>-11,63; 15,43</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 10,97</t>
+          <t>-12,27; 10,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17,45; 43,39</t>
+          <t>18,37; 44,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 18,96</t>
+          <t>-6,83; 18,45</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 9,7</t>
+          <t>-14,46; 9,91</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,18; 54,75</t>
+          <t>28,96; 56,18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 12,23</t>
+          <t>-4,97; 13,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 6,92</t>
+          <t>-11,34; 6,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>26,77; 46,54</t>
+          <t>27,17; 45,32</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,52</t>
+          <t>2,07; 5,46</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,54</t>
+          <t>0,14; 3,63</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8,72; 18,08</t>
+          <t>8,78; 17,98</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,21</t>
+          <t>0,56; 4,36</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,34</t>
+          <t>-0,35; 3,48</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>19,03; 34,67</t>
+          <t>18,64; 34,33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,41</t>
+          <t>1,87; 4,4</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,85</t>
+          <t>0,37; 2,85</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>15,72; 25,55</t>
+          <t>15,95; 25,34</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>12,08; 41,7</t>
+          <t>14,3; 43,22</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1,03; 27,47</t>
+          <t>0,89; 27,72</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>64,99; 135,45</t>
+          <t>65,13; 136,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2,69; 28,77</t>
+          <t>3,55; 29,74</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 22,62</t>
+          <t>-2,03; 23,53</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>117,58; 225,88</t>
+          <t>113,01; 222,75</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,77; 30,65</t>
+          <t>12,12; 30,69</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2,22; 19,99</t>
+          <t>2,44; 19,97</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>102,76; 171,68</t>
+          <t>104,16; 173,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P37-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P37-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>9,55</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>4,38</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 5,74</t>
+          <t>-0,38; 5,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,56</t>
+          <t>-1,12; 4,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 5,08</t>
+          <t>-3,05; 3,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,12</t>
+          <t>-1,14; 3,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,83</t>
+          <t>-1,0; 3,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 16,43</t>
+          <t>5,45; 15,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,83</t>
+          <t>-0,15; 3,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,42</t>
+          <t>-0,3; 3,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 8,18</t>
+          <t>1,75; 7,84</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>-6,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>412,43%</t>
+          <t>389,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>150,65%</t>
+          <t>143,95%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 237,77</t>
+          <t>-10,74; 215,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 188,44</t>
+          <t>-26,51; 180,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,21; 192,83</t>
+          <t>-68,45; 171,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,6; 205,43</t>
+          <t>-34,96; 249,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 263,01</t>
+          <t>-34,75; 247,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>155,3; 1050,02</t>
+          <t>152,98; 1017,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 168,41</t>
+          <t>-5,45; 165,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 143,19</t>
+          <t>-8,33; 147,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,73; 348,25</t>
+          <t>39,93; 312,52</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>6,61</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,77</t>
+          <t>12,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,8</t>
+          <t>9,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,05</t>
+          <t>-0,86; 3,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,89</t>
+          <t>-2,63; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 11,57</t>
+          <t>3,19; 11,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,09</t>
+          <t>-0,82; 3,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,84</t>
+          <t>-1,79; 2,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 15,38</t>
+          <t>8,54; 16,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,07</t>
+          <t>-0,3; 3,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,58</t>
+          <t>-1,78; 1,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 12,24</t>
+          <t>6,84; 12,49</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145,31%</t>
+          <t>146,06%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>287,12%</t>
+          <t>332,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>211,14%</t>
+          <t>229,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 124,75</t>
+          <t>-15,26; 109,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,41; 54,65</t>
+          <t>-49,92; 56,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,54; 303,31</t>
+          <t>55,25; 305,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 160,02</t>
+          <t>-17,96; 142,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 120,08</t>
+          <t>-36,85; 106,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>109,85; 553,12</t>
+          <t>166,86; 647,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 85,93</t>
+          <t>-6,28; 93,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 48,13</t>
+          <t>-36,0; 43,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>117,95; 340,66</t>
+          <t>137,24; 349,03</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>9,44</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,05</t>
+          <t>9,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,64</t>
+          <t>-0,78; 4,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; -0,68</t>
+          <t>-4,98; -0,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,09</t>
+          <t>5,71; 13,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,51</t>
+          <t>-1,84; 3,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,73</t>
+          <t>-2,74; 3,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,91</t>
+          <t>6,56; 12,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,22</t>
+          <t>-0,63; 3,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,18</t>
+          <t>-3,25; 0,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,32</t>
+          <t>6,98; 11,8</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188,81%</t>
+          <t>172,67%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>151,83%</t>
+          <t>144,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>167,96%</t>
+          <t>156,8%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 111,61</t>
+          <t>-12,27; 113,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,49; -11,79</t>
+          <t>-74,5; -10,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98,07; 340,88</t>
+          <t>83,13; 306,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 65,28</t>
+          <t>-24,67; 72,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,43; 52,39</t>
+          <t>-34,84; 57,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,12; 249,56</t>
+          <t>84,19; 247,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 64,16</t>
+          <t>-9,39; 69,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,52; 3,8</t>
+          <t>-46,74; 8,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>108,34; 244,84</t>
+          <t>98,18; 231,55</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>13,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,56</t>
+          <t>17,51</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,6</t>
+          <t>15,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,49</t>
+          <t>-2,5; 4,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 3,62</t>
+          <t>-2,79; 3,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 14,57</t>
+          <t>9,18; 16,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,97</t>
+          <t>-0,81; 5,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,88</t>
+          <t>-0,9; 4,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,11; 19,96</t>
+          <t>14,29; 20,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,0</t>
+          <t>-0,48; 4,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,19</t>
+          <t>-1,02; 3,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 15,75</t>
+          <t>12,89; 17,9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>174,92%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>323,5%</t>
+          <t>342,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>184,65%</t>
+          <t>243,33%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 81,04</t>
+          <t>-29,5; 73,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 62,56</t>
+          <t>-29,84; 61,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 229,77</t>
+          <t>95,6; 303,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 132,64</t>
+          <t>-15,88; 135,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 128,39</t>
+          <t>-15,6; 109,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>168,87; 527,07</t>
+          <t>211,41; 550,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 77,66</t>
+          <t>-8,04; 75,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 62,03</t>
+          <t>-14,49; 62,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58,01; 280,79</t>
+          <t>166,12; 355,27</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18,28</t>
+          <t>18,08</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,39</t>
+          <t>19,65</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18,84</t>
+          <t>18,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 6,34</t>
+          <t>-5,06; 6,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 5,81</t>
+          <t>-4,46; 5,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,15; 23,69</t>
+          <t>12,71; 23,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 6,84</t>
+          <t>-3,79; 6,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 4,73</t>
+          <t>-6,09; 4,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,2; 23,88</t>
+          <t>14,76; 24,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 5,12</t>
+          <t>-2,39; 5,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,71</t>
+          <t>-3,82; 3,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,0; 22,22</t>
+          <t>15,3; 22,7</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>109,79%</t>
+          <t>111,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>104,27%</t>
+          <t>104,44%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 39,44</t>
+          <t>-23,09; 40,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 36,88</t>
+          <t>-21,57; 35,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58,65; 152,37</t>
+          <t>58,45; 155,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 44,95</t>
+          <t>-19,05; 44,12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 31,29</t>
+          <t>-29,9; 26,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,21; 164,72</t>
+          <t>66,75; 161,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 32,98</t>
+          <t>-12,13; 31,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 22,93</t>
+          <t>-19,29; 22,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>72,95; 143,15</t>
+          <t>75,79; 145,68</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33,54</t>
+          <t>32,57</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,04</t>
+          <t>29,52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36,73</t>
+          <t>30,89</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>9,92; 25,94</t>
+          <t>9,4; 25,82</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 14,88</t>
+          <t>-0,95; 15,7</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26,34; 40,28</t>
+          <t>25,89; 39,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 10,68</t>
+          <t>-4,74; 10,19</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 5,63</t>
+          <t>-8,58; 5,57</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,78; 51,13</t>
+          <t>23,21; 35,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,6; 15,59</t>
+          <t>4,8; 15,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 7,78</t>
+          <t>-2,9; 7,57</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>29,59; 47,55</t>
+          <t>26,41; 35,12</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22,66; 74,86</t>
+          <t>22,01; 73,8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 43,11</t>
+          <t>-2,33; 44,48</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>59,54; 115,29</t>
+          <t>58,54; 113,79</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 26,08</t>
+          <t>-9,83; 25,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 13,98</t>
+          <t>-18,15; 13,39</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>58,18; 134,04</t>
+          <t>46,55; 88,7</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,18; 39,16</t>
+          <t>10,77; 40,01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 19,49</t>
+          <t>-6,49; 19,64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>68,06; 123,26</t>
+          <t>57,3; 89,4</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20,11</t>
+          <t>20,01</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,91</t>
+          <t>24,95</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23,08</t>
+          <t>23,07</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 9,82</t>
+          <t>-7,59; 10,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 6,43</t>
+          <t>-9,43; 7,58</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13,61; 27,69</t>
+          <t>13,07; 27,62</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 10,49</t>
+          <t>-4,4; 11,02</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 5,67</t>
+          <t>-10,08; 5,88</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,34; 31,6</t>
+          <t>18,44; 30,89</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 8,11</t>
+          <t>-3,42; 7,64</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 4,2</t>
+          <t>-7,25; 4,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18,45; 27,48</t>
+          <t>18,76; 27,9</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 15,43</t>
+          <t>-10,68; 17,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 10,18</t>
+          <t>-13,03; 12,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18,37; 44,6</t>
+          <t>17,68; 44,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 18,45</t>
+          <t>-6,66; 19,04</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 9,91</t>
+          <t>-15,48; 10,35</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,96; 56,18</t>
+          <t>27,38; 54,57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 13,57</t>
+          <t>-5,02; 12,51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 6,93</t>
+          <t>-10,94; 7,11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>27,17; 45,32</t>
+          <t>27,55; 46,52</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>17,04</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,19</t>
+          <t>20,14</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>19,28</t>
+          <t>18,65</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,46</t>
+          <t>1,81; 5,42</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,63</t>
+          <t>0,29; 3,57</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8,78; 17,98</t>
+          <t>15,07; 19,08</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,36</t>
+          <t>0,6; 4,2</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,48</t>
+          <t>-0,58; 3,36</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,64; 34,33</t>
+          <t>18,28; 22,21</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,4</t>
+          <t>1,75; 4,3</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,85</t>
+          <t>0,32; 2,83</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>15,95; 25,34</t>
+          <t>17,32; 20,0</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>108,98%</t>
+          <t>122,81%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>146,28%</t>
+          <t>127,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>129,58%</t>
+          <t>125,33%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>14,3; 43,22</t>
+          <t>12,15; 41,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0,89; 27,72</t>
+          <t>2,07; 27,78</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>65,13; 136,27</t>
+          <t>101,39; 146,65</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3,55; 29,74</t>
+          <t>3,08; 27,48</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 23,53</t>
+          <t>-3,42; 22,43</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>113,01; 222,75</t>
+          <t>108,86; 150,15</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,12; 30,69</t>
+          <t>11,45; 30,45</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2,44; 19,97</t>
+          <t>1,99; 19,85</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>104,16; 173,49</t>
+          <t>109,33; 139,98</t>
         </is>
       </c>
     </row>
